--- a/grupos/3AEM - Estadisticos 20241.xlsx
+++ b/grupos/3AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="114">
   <si>
     <t>Materia</t>
   </si>
@@ -173,24 +173,24 @@
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -203,139 +203,163 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BERULES</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
+    <t>CERONIO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>JUSTO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>SANTOS</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BERULES</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>UTRERA</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ATLAHUA</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>NEGRETE</t>
   </si>
   <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>JOSUE YAHIR</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
   </si>
   <si>
     <t>ERICK ANGEL</t>
   </si>
   <si>
+    <t>VICENTE ABIMAEL</t>
+  </si>
+  <si>
+    <t>DANA INGRID</t>
+  </si>
+  <si>
     <t>OMAR DAVID</t>
   </si>
   <si>
-    <t>JUAN SEBASTIAN</t>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>FELIX</t>
+  </si>
+  <si>
+    <t>DANILO</t>
   </si>
   <si>
     <t>JAQUELINE</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
     <t>JOEL MIGUEL</t>
-  </si>
-  <si>
-    <t>VICENTE ABIMAEL</t>
-  </si>
-  <si>
-    <t>DANA INGRID</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>FELIX</t>
-  </si>
-  <si>
-    <t>DANILO</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
   </si>
 </sst>
 </file>
@@ -881,28 +905,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -944,7 +968,7 @@
         <v>10</v>
       </c>
       <c r="AE4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4">
         <v>10</v>
@@ -982,28 +1006,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1042,10 +1066,10 @@
         <v>10</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF5">
         <v>9</v>
@@ -1083,28 +1107,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1143,10 +1167,10 @@
         <v>10</v>
       </c>
       <c r="AD6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF6">
         <v>10</v>
@@ -1184,28 +1208,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1232,25 +1256,25 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>8</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG7">
         <v>-1</v>
@@ -1285,28 +1309,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1348,7 +1372,7 @@
         <v>10</v>
       </c>
       <c r="AE8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF8">
         <v>10</v>
@@ -1386,28 +1410,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1440,16 +1464,16 @@
         <v>6</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>5</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF9">
         <v>7</v>
@@ -1487,28 +1511,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1535,25 +1559,25 @@
         <v>-1</v>
       </c>
       <c r="Z10">
+        <v>5</v>
+      </c>
+      <c r="AA10">
+        <v>8</v>
+      </c>
+      <c r="AB10">
         <v>6</v>
       </c>
-      <c r="AA10">
-        <v>8</v>
-      </c>
-      <c r="AB10">
-        <v>7</v>
-      </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>-1</v>
@@ -1588,28 +1612,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1648,10 +1672,10 @@
         <v>9</v>
       </c>
       <c r="AD11">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF11">
         <v>9</v>
@@ -1689,28 +1713,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1749,10 +1773,10 @@
         <v>10</v>
       </c>
       <c r="AD12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF12">
         <v>10</v>
@@ -1790,28 +1814,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1847,13 +1871,13 @@
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF13">
         <v>10</v>
@@ -1891,28 +1915,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1954,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="AE14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF14">
         <v>10</v>
@@ -1992,28 +2016,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2049,13 +2073,13 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF15">
         <v>8</v>
@@ -2093,28 +2117,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2141,22 +2165,22 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA16">
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF16">
         <v>9</v>
@@ -2194,28 +2218,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2251,16 +2275,16 @@
         <v>5</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG17">
         <v>-1</v>
@@ -2295,28 +2319,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2355,13 +2379,13 @@
         <v>5</v>
       </c>
       <c r="AD18">
+        <v>7</v>
+      </c>
+      <c r="AE18">
+        <v>7</v>
+      </c>
+      <c r="AF18">
         <v>6</v>
-      </c>
-      <c r="AE18">
-        <v>5</v>
-      </c>
-      <c r="AF18">
-        <v>5</v>
       </c>
       <c r="AG18">
         <v>-1</v>
@@ -2396,28 +2420,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2453,13 +2477,13 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD19">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF19">
         <v>9</v>
@@ -2497,28 +2521,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2554,16 +2578,16 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>-1</v>
@@ -2598,28 +2622,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2646,22 +2670,22 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>7</v>
       </c>
       <c r="AB21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF21">
         <v>10</v>
@@ -2699,28 +2723,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2759,10 +2783,10 @@
         <v>10</v>
       </c>
       <c r="AD22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE22">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF22">
         <v>9</v>
@@ -2800,28 +2824,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2848,22 +2872,22 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA23">
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF23">
         <v>9</v>
@@ -2901,28 +2925,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2955,16 +2979,16 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC24">
         <v>5</v>
       </c>
       <c r="AD24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF24">
         <v>5</v>
@@ -3002,28 +3026,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3050,25 +3074,25 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>8</v>
       </c>
       <c r="AB25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>5</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>-1</v>
@@ -3103,28 +3127,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3160,13 +3184,13 @@
         <v>10</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AF26">
         <v>10</v>
@@ -3204,28 +3228,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3252,7 +3276,7 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <v>8</v>
@@ -3264,13 +3288,13 @@
         <v>5</v>
       </c>
       <c r="AD27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG27">
         <v>-1</v>
@@ -3451,7 +3475,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3475,7 +3499,7 @@
         <v>100</v>
       </c>
       <c r="V4">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="W4">
         <v>100</v>
@@ -3525,13 +3549,13 @@
         <v>100</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N5">
-        <v>95.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O5">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3549,13 +3573,13 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="V5">
-        <v>95.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="W5">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="X5">
         <v>100</v>
@@ -3682,13 +3706,13 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O7">
-        <v>96.8</v>
+        <v>99.2</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3706,13 +3730,13 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="W7">
-        <v>96.8</v>
+        <v>99.2</v>
       </c>
       <c r="X7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -3759,7 +3783,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3783,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="W8">
         <v>100</v>
@@ -3824,7 +3848,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -3833,13 +3857,13 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="N9">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O9">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3848,7 +3872,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3857,13 +3881,13 @@
         <v>100</v>
       </c>
       <c r="U9">
-        <v>88.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="V9">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="W9">
-        <v>95.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -3919,7 +3943,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3943,7 +3967,7 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -3990,10 +4014,10 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O11">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -4014,10 +4038,10 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="W11">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -4067,13 +4091,13 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="O12">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>90.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4091,13 +4115,13 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="W12">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="X12">
-        <v>90.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -4141,13 +4165,13 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N13">
-        <v>95.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O13">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4165,13 +4189,13 @@
         <v>100</v>
       </c>
       <c r="U13">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V13">
-        <v>95.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="W13">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -4221,10 +4245,10 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O14">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4245,10 +4269,10 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="W14">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="X14">
         <v>100</v>
@@ -4298,13 +4322,13 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="O15">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P15">
-        <v>90.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4322,13 +4346,13 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="W15">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="X15">
-        <v>90.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="Y15">
         <v>100</v>
@@ -4372,10 +4396,10 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4396,10 +4420,10 @@
         <v>100</v>
       </c>
       <c r="U16">
-        <v>94.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="W16">
         <v>100</v>
@@ -4446,19 +4470,19 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>50</v>
+        <v>56.3</v>
       </c>
       <c r="M17">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="N17">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="O17">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4470,19 +4494,19 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>50</v>
+        <v>56.3</v>
       </c>
       <c r="U17">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="V17">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="W17">
-        <v>96.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="X17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -4526,13 +4550,13 @@
         <v>62.5</v>
       </c>
       <c r="M18">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N18">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O18">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4550,13 +4574,13 @@
         <v>62.5</v>
       </c>
       <c r="U18">
-        <v>94.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V18">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="W18">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="X18">
         <v>100</v>
@@ -4606,10 +4630,10 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="P19">
         <v>100</v>
@@ -4630,10 +4654,10 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="W19">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="X19">
         <v>100</v>
@@ -4683,13 +4707,13 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>91.7</v>
+        <v>91.5</v>
       </c>
       <c r="O20">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4707,13 +4731,13 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>91.7</v>
+        <v>91.5</v>
       </c>
       <c r="W20">
-        <v>98.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -4760,10 +4784,10 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -4784,10 +4808,10 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>91.7</v>
+        <v>95.7</v>
       </c>
       <c r="W21">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="X21">
         <v>100</v>
@@ -4837,10 +4861,10 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="P22">
         <v>100</v>
@@ -4861,10 +4885,10 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="X22">
         <v>100</v>
@@ -4914,10 +4938,10 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>95.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O23">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P23">
         <v>100</v>
@@ -4938,10 +4962,10 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>95.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="W23">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="X23">
         <v>100</v>
@@ -4988,16 +5012,16 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N24">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O24">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="P24">
-        <v>81.8</v>
+        <v>70</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -5012,16 +5036,16 @@
         <v>100</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="V24">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="W24">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
       <c r="X24">
-        <v>81.8</v>
+        <v>70</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -5056,7 +5080,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -5065,22 +5089,22 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N25">
         <v>100</v>
       </c>
       <c r="O25">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5089,16 +5113,16 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="V25">
         <v>100</v>
       </c>
       <c r="W25">
-        <v>96.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="X25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -5145,7 +5169,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5169,7 +5193,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="W26">
         <v>100</v>
@@ -5219,16 +5243,16 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>88.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="O27">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5243,16 +5267,16 @@
         <v>100</v>
       </c>
       <c r="U27">
-        <v>88.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="W27">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="X27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Y27">
         <v>100</v>
@@ -5341,7 +5365,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
@@ -5350,19 +5374,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>41.7</v>
+        <v>79.2</v>
       </c>
       <c r="G3" s="2">
-        <v>58.3</v>
+        <v>20.8</v>
       </c>
       <c r="H3">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5373,7 +5397,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
@@ -5394,7 +5418,7 @@
         <v>20.8</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5405,7 +5429,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -5414,19 +5438,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>83.3</v>
+        <v>87.5</v>
       </c>
       <c r="G5" s="2">
-        <v>16.7</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5446,19 +5470,19 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G6" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5469,7 +5493,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>55</v>
@@ -5478,16 +5502,16 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>91.7</v>
+        <v>95.8</v>
       </c>
       <c r="G7" s="2">
-        <v>8.300000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="H7">
         <v>8.300000000000001</v>
@@ -5501,7 +5525,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>56</v>
@@ -5510,19 +5534,19 @@
         <v>24</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5533,10 +5557,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>24</v>
@@ -5554,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -5604,7 +5628,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5636,19 +5660,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920003</v>
+        <v>23330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>51</v>
@@ -5659,16 +5683,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920003</v>
+        <v>23330051920006</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -5682,22 +5706,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920005</v>
+        <v>23330051920008</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5705,16 +5729,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920005</v>
+        <v>23330051920008</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -5728,22 +5752,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920008</v>
+        <v>23330051920018</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5751,16 +5775,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920008</v>
+        <v>23330051920018</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -5774,19 +5798,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920014</v>
+        <v>23330051920023</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -5797,16 +5821,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920014</v>
+        <v>23330051920023</v>
       </c>
       <c r="B9" t="s">
         <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -5820,19 +5844,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920021</v>
+        <v>23330051920025</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>51</v>
@@ -5843,16 +5867,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920021</v>
+        <v>23330051920025</v>
       </c>
       <c r="B11" t="s">
         <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E11" t="s">
         <v>12</v>
@@ -5866,39 +5890,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920020</v>
+        <v>23330051920003</v>
       </c>
       <c r="B12" t="s">
         <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920020</v>
+        <v>23330051920002</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -5912,39 +5936,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920024</v>
+        <v>23330051920004</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920024</v>
+        <v>23330051920005</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -5958,16 +5982,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920002</v>
+        <v>23330051920182</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
         <v>12</v>
@@ -5981,16 +6005,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920004</v>
+        <v>23330051920009</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
         <v>12</v>
@@ -6004,16 +6028,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920182</v>
+        <v>23330051920026</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E18" t="s">
         <v>12</v>
@@ -6027,16 +6051,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920009</v>
+        <v>23330051920010</v>
       </c>
       <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" t="s">
         <v>71</v>
       </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
       <c r="D19" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E19" t="s">
         <v>12</v>
@@ -6050,16 +6074,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920026</v>
+        <v>23330051920012</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
         <v>12</v>
@@ -6073,16 +6097,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920010</v>
+        <v>23330051920013</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
         <v>12</v>
@@ -6096,16 +6120,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920012</v>
+        <v>23330051920014</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
         <v>12</v>
@@ -6119,16 +6143,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920013</v>
+        <v>23330051920204</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E23" t="s">
         <v>12</v>
@@ -6142,16 +6166,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920204</v>
+        <v>23330051920321</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E24" t="s">
         <v>12</v>
@@ -6165,13 +6189,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920321</v>
+        <v>23330051920021</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D25" t="s">
         <v>105</v>
@@ -6183,6 +6207,52 @@
         <v>50</v>
       </c>
       <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920020</v>
+      </c>
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>50</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920024</v>
+      </c>
+      <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20241.xlsx
+++ b/grupos/3AEM - Estadisticos 20241.xlsx
@@ -908,7 +908,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -956,7 +956,7 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
@@ -1009,7 +1009,7 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
         <v>10</v>
@@ -1057,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB5">
         <v>10</v>
@@ -1110,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
         <v>7</v>
@@ -1211,7 +1211,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>8</v>
@@ -1259,7 +1259,7 @@
         <v>7</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB7">
         <v>8</v>
@@ -1312,7 +1312,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>10</v>
@@ -1360,7 +1360,7 @@
         <v>10</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1413,7 +1413,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -1461,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>6</v>
@@ -1514,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1562,7 +1562,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB10">
         <v>6</v>
@@ -1615,7 +1615,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1716,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1817,7 +1817,7 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1966,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -2019,7 +2019,7 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>10</v>
@@ -2067,7 +2067,7 @@
         <v>9</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -2120,7 +2120,7 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -2168,7 +2168,7 @@
         <v>9</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2221,7 +2221,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -2269,7 +2269,7 @@
         <v>5</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>5</v>
@@ -2322,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -2370,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB18">
         <v>5</v>
@@ -2423,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
         <v>10</v>
@@ -2471,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB19">
         <v>10</v>
@@ -2524,7 +2524,7 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>7</v>
@@ -2572,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>7</v>
@@ -2625,7 +2625,7 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2673,7 +2673,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>6</v>
@@ -2726,7 +2726,7 @@
         <v>9</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2774,7 +2774,7 @@
         <v>10</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB22">
         <v>10</v>
@@ -2827,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>10</v>
@@ -2875,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -2928,7 +2928,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -2976,7 +2976,7 @@
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -3029,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>6</v>
@@ -3077,7 +3077,7 @@
         <v>7</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>7</v>
@@ -3130,7 +3130,7 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>10</v>
@@ -3178,7 +3178,7 @@
         <v>10</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -3231,7 +3231,7 @@
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
         <v>7</v>
@@ -3279,7 +3279,7 @@
         <v>7</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -5502,19 +5502,19 @@
         <v>24</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3AEM - Estadisticos 20241.xlsx
+++ b/grupos/3AEM - Estadisticos 20241.xlsx
@@ -185,7 +185,7 @@
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
+    <t>Martínez Marañon Mauricio</t>
   </si>
   <si>
     <t>Torres Sánchez José Luis</t>

--- a/grupos/3AEM - Estadisticos 20241.xlsx
+++ b/grupos/3AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -203,6 +203,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -221,6 +227,12 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -231,6 +243,12 @@
   </si>
   <si>
     <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
   </si>
   <si>
     <t>JUAN YAHEL</t>
@@ -4976,7 +4994,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5008,16 +5026,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920015</v>
+        <v>23330051920022</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5031,16 +5049,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920015</v>
+        <v>23330051920022</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5054,16 +5072,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920006</v>
+        <v>23330051920022</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5077,22 +5095,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920008</v>
+        <v>23330051920022</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5100,16 +5118,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920018</v>
+        <v>23330051920017</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -5123,22 +5141,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920023</v>
+        <v>23330051920017</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5146,10 +5164,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920025</v>
+        <v>23330051920017</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
@@ -5164,6 +5182,167 @@
         <v>50</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920015</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920015</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920006</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920008</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920018</v>
+      </c>
+      <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920023</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20241.xlsx
+++ b/grupos/3AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -203,21 +203,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>TELLO</t>
   </si>
   <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -227,15 +224,15 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>UTRERA</t>
   </si>
   <si>
@@ -245,19 +242,16 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>JUAN YAHEL</t>
+  </si>
+  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
-    <t>ANGEL YAMIL</t>
-  </si>
-  <si>
-    <t>JUAN YAHEL</t>
-  </si>
-  <si>
     <t>RAFAEL FELIPE</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
   </si>
   <si>
     <t>CARLOS DAVID</t>
@@ -814,34 +808,34 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z4">
         <v>10</v>
@@ -850,10 +844,10 @@
         <v>10</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -903,25 +897,25 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -936,7 +930,7 @@
         <v>10</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB5">
         <v>8</v>
@@ -992,25 +986,25 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1019,7 +1013,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>10</v>
@@ -1081,34 +1075,34 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>6</v>
@@ -1120,7 +1114,7 @@
         <v>7</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1170,25 +1164,25 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1259,31 +1253,31 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1348,34 +1342,34 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1384,10 +1378,10 @@
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1437,25 +1431,25 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1473,7 +1467,7 @@
         <v>9</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC11">
         <v>9</v>
@@ -1526,25 +1520,25 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1615,25 +1609,25 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1704,25 +1698,25 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1793,34 +1787,34 @@
         <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <v>7</v>
@@ -1832,7 +1826,7 @@
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1882,28 +1876,28 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1915,13 +1909,13 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>7</v>
       </c>
       <c r="AC16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1971,25 +1965,25 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2004,13 +1998,13 @@
         <v>6</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2060,25 +2054,25 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2093,10 +2087,10 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>6</v>
@@ -2149,25 +2143,25 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2238,34 +2232,34 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>6</v>
@@ -2277,7 +2271,7 @@
         <v>7</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2327,40 +2321,40 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2416,28 +2410,28 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2449,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>8</v>
@@ -2505,25 +2499,25 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2541,7 +2535,7 @@
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC23">
         <v>9</v>
@@ -2594,46 +2588,46 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>5</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>5</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2683,46 +2677,46 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2772,28 +2766,28 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2805,7 +2799,7 @@
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -2861,28 +2855,28 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2894,13 +2888,13 @@
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3084,7 +3078,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -3152,10 +3146,10 @@
         <v>97</v>
       </c>
       <c r="T5">
-        <v>93.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3220,7 +3214,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3276,7 +3270,7 @@
         <v>95</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3288,13 +3282,13 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>93.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="U7">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="V7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -3356,7 +3350,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95.7</v>
+        <v>97.2</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -3412,7 +3406,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3424,10 +3418,10 @@
         <v>84.8</v>
       </c>
       <c r="T9">
-        <v>93.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="U9">
-        <v>98.40000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3480,7 +3474,7 @@
         <v>95</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3495,10 +3489,10 @@
         <v>100</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3560,10 +3554,10 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U11">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -3628,13 +3622,13 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95.7</v>
+        <v>97.2</v>
       </c>
       <c r="U12">
         <v>100</v>
       </c>
       <c r="V12">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3696,10 +3690,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T13">
-        <v>93.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -3764,10 +3758,10 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U14">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -3820,7 +3814,7 @@
         <v>95</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3832,13 +3826,13 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="U15">
-        <v>97.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="V15">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3888,7 +3882,7 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -3900,7 +3894,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="T16">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -3956,25 +3950,25 @@
         <v>80</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q17">
         <v>100</v>
       </c>
       <c r="R17">
-        <v>56.3</v>
+        <v>58.3</v>
       </c>
       <c r="S17">
         <v>72.7</v>
       </c>
       <c r="T17">
-        <v>95.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="U17">
-        <v>97.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V17">
-        <v>80</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -4024,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>82.8</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4036,10 +4030,10 @@
         <v>90.90000000000001</v>
       </c>
       <c r="T18">
-        <v>97.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="U18">
-        <v>99.2</v>
+        <v>93.5</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -4104,10 +4098,10 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U19">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4160,7 +4154,7 @@
         <v>80</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4172,13 +4166,13 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>91.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="U20">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V20">
-        <v>80</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -4228,7 +4222,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4240,10 +4234,10 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>95.7</v>
+        <v>97.2</v>
       </c>
       <c r="U21">
-        <v>99.2</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4296,7 +4290,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -4308,10 +4302,10 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U22">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4376,7 +4370,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>93.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="U23">
         <v>98.40000000000001</v>
@@ -4432,7 +4426,7 @@
         <v>70</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4444,13 +4438,13 @@
         <v>87.90000000000001</v>
       </c>
       <c r="T24">
-        <v>93.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U24">
         <v>96.7</v>
       </c>
       <c r="V24">
-        <v>70</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4500,7 +4494,7 @@
         <v>95</v>
       </c>
       <c r="P25">
-        <v>95</v>
+        <v>82.8</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -4515,10 +4509,10 @@
         <v>100</v>
       </c>
       <c r="U25">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="V25">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -4580,10 +4574,10 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>97.90000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -4636,7 +4630,7 @@
         <v>95</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4648,13 +4642,13 @@
         <v>78.8</v>
       </c>
       <c r="T27">
-        <v>95.7</v>
+        <v>95.8</v>
       </c>
       <c r="U27">
-        <v>99.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V27">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4752,19 +4746,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>79.2</v>
+        <v>83.3</v>
       </c>
       <c r="G3" s="2">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4784,16 +4778,16 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="G4" s="2">
-        <v>12.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4">
         <v>8.1</v>
@@ -4816,19 +4810,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4892,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4994,7 +4988,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5026,16 +5020,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920022</v>
+        <v>23330051920017</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5049,16 +5043,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920022</v>
+        <v>23330051920017</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5072,16 +5066,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920022</v>
+        <v>23330051920017</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5095,10 +5089,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920022</v>
+        <v>23330051920015</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
         <v>69</v>
@@ -5107,10 +5101,10 @@
         <v>75</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5118,22 +5112,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5141,10 +5135,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920017</v>
+        <v>23330051920022</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
@@ -5153,10 +5147,10 @@
         <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5164,10 +5158,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920017</v>
+        <v>23330051920022</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
         <v>70</v>
@@ -5187,22 +5181,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920015</v>
+        <v>23330051920006</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
         <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5210,22 +5204,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920015</v>
+        <v>23330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
         <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5233,16 +5227,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920006</v>
+        <v>23330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -5256,93 +5250,24 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920008</v>
+        <v>23330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920018</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920023</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920025</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20241.xlsx
+++ b/grupos/3AEM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -203,58 +203,52 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MONTERD</t>
   </si>
   <si>
-    <t>LUNA</t>
+    <t>RAMOS</t>
   </si>
   <si>
     <t>TELLO</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>VASQUEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>UTRERA</t>
   </si>
   <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>UTRERA</t>
-  </si>
-  <si>
     <t>ESPINDOLA</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>JUAN YAHEL</t>
+  </si>
+  <si>
     <t>ANGEL YAMIL</t>
   </si>
   <si>
-    <t>JUAN YAHEL</t>
+    <t>CARLOS DAVID</t>
   </si>
   <si>
     <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>RAFAEL FELIPE</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
   </si>
   <si>
     <t>JOSUE YAHIR</t>
@@ -817,7 +811,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -906,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -995,7 +989,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1084,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1105,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1173,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1262,7 +1256,7 @@
         <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1283,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA9">
         <v>7</v>
@@ -1351,7 +1345,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1372,7 +1366,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1440,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1529,7 +1523,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1618,7 +1612,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1707,7 +1701,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1796,7 +1790,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1817,7 +1811,7 @@
         <v>9</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1885,7 +1879,7 @@
         <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1974,7 +1968,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1995,7 +1989,7 @@
         <v>5</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <v>6</v>
@@ -2063,7 +2057,7 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -2152,7 +2146,7 @@
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2173,7 +2167,7 @@
         <v>10</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>9</v>
@@ -2241,7 +2235,7 @@
         <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2262,7 +2256,7 @@
         <v>6</v>
       </c>
       <c r="Z20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <v>8</v>
@@ -2330,7 +2324,7 @@
         <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2419,7 +2413,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2508,7 +2502,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2529,7 +2523,7 @@
         <v>9</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2597,7 +2591,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2618,7 +2612,7 @@
         <v>7</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>8</v>
@@ -2686,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2775,7 +2769,7 @@
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2864,7 +2858,7 @@
         <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -3075,7 +3069,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T4">
         <v>98.59999999999999</v>
@@ -3143,7 +3137,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>97</v>
+        <v>91.7</v>
       </c>
       <c r="T5">
         <v>95.8</v>
@@ -3211,7 +3205,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T6">
         <v>98.59999999999999</v>
@@ -3415,7 +3409,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>84.8</v>
+        <v>83.3</v>
       </c>
       <c r="T9">
         <v>93.09999999999999</v>
@@ -3483,7 +3477,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -3619,7 +3613,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T12">
         <v>97.2</v>
@@ -3687,7 +3681,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>93.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T13">
         <v>95.8</v>
@@ -3891,7 +3885,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="T16">
         <v>95.8</v>
@@ -3959,7 +3953,7 @@
         <v>58.3</v>
       </c>
       <c r="S17">
-        <v>72.7</v>
+        <v>54.2</v>
       </c>
       <c r="T17">
         <v>81.90000000000001</v>
@@ -4027,7 +4021,7 @@
         <v>62.5</v>
       </c>
       <c r="S18">
-        <v>90.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="T18">
         <v>83.3</v>
@@ -4095,7 +4089,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T19">
         <v>98.59999999999999</v>
@@ -4163,7 +4157,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="T20">
         <v>93.09999999999999</v>
@@ -4231,7 +4225,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T21">
         <v>97.2</v>
@@ -4367,7 +4361,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T23">
         <v>95.8</v>
@@ -4435,7 +4429,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>87.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="T24">
         <v>94.40000000000001</v>
@@ -4503,7 +4497,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>93.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -4571,7 +4565,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T26">
         <v>98.59999999999999</v>
@@ -4639,7 +4633,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>78.8</v>
+        <v>58.3</v>
       </c>
       <c r="T27">
         <v>95.8</v>
@@ -4726,7 +4720,7 @@
         <v>20.8</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5020,16 +5014,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5043,16 +5037,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5066,16 +5060,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920017</v>
+        <v>23330051920015</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5089,16 +5083,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920015</v>
+        <v>23330051920017</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -5112,16 +5106,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920015</v>
+        <v>23330051920017</v>
       </c>
       <c r="B6" t="s">
         <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5135,22 +5129,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920022</v>
+        <v>23330051920017</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5158,22 +5152,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920022</v>
+        <v>23330051920018</v>
       </c>
       <c r="B8" t="s">
         <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5181,16 +5175,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920006</v>
+        <v>23330051920018</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5204,16 +5198,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920018</v>
+        <v>23330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -5230,13 +5224,13 @@
         <v>23330051920023</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -5253,13 +5247,13 @@
         <v>23330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
